--- a/inventory/files/2026-W42/STA_CA_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_CA_AUTO_2026-W42.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="14" min="1" max="1"/>
@@ -1694,66 +1694,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1948</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-REPAIRHL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>611</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-MFDRYTWLA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AH-VEHSHAM16A</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AH-REPAIRHL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AH-MFDRYTWLA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
         <v>3</v>
       </c>
     </row>
